--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,21 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64F7159-749D-4353-A10E-31509A33B5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5044C588-AF2B-4724-A136-31A1FF922EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DMartDataset" sheetId="1" r:id="rId1"/>
     <sheet name="Flashfill" sheetId="3" r:id="rId2"/>
     <sheet name="Customlist" sheetId="4" r:id="rId3"/>
     <sheet name="IF,Iferror" sheetId="8" r:id="rId4"/>
-    <sheet name="Sheet8" sheetId="9" r:id="rId5"/>
-    <sheet name="Lookup" sheetId="10" r:id="rId6"/>
+    <sheet name="Subtotal" sheetId="9" r:id="rId5"/>
+    <sheet name="VLOOKUP" sheetId="10" r:id="rId6"/>
+    <sheet name="HLOOKUP" sheetId="11" r:id="rId7"/>
+    <sheet name="indirect" sheetId="12" r:id="rId8"/>
+    <sheet name="Data Validation" sheetId="13" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet8!$A$1:$A$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Subtotal!$A$1:$A$8</definedName>
+    <definedName name="Apples">indirect!$N$2:$N$6</definedName>
     <definedName name="Customertype">DMart_Sales_Data[customer_type]</definedName>
+    <definedName name="Lemons">indirect!$P$2:$P$6</definedName>
     <definedName name="Orderdate">DMart_Sales_Data[order_date]</definedName>
     <definedName name="Orders">DMart_Sales_Data[OrderID]</definedName>
     <definedName name="PaymentMode">DMart_Sales_Data[payment_mode]</definedName>
@@ -67,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4202" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4256" uniqueCount="709">
   <si>
     <t>Region</t>
   </si>
@@ -2101,6 +2106,99 @@
   </si>
   <si>
     <t>Using Index Match</t>
+  </si>
+  <si>
+    <t>using 1</t>
+  </si>
+  <si>
+    <t>usinng 9</t>
+  </si>
+  <si>
+    <t>using 101</t>
+  </si>
+  <si>
+    <t>using 109</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Sales Value using VLOOKUP</t>
+  </si>
+  <si>
+    <t>Values Using HLOOKUP</t>
+  </si>
+  <si>
+    <t>anish</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>R7C1</t>
+  </si>
+  <si>
+    <t>concatenation operator</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>Apples</t>
+  </si>
+  <si>
+    <t>Bananas</t>
+  </si>
+  <si>
+    <t>Lemons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fruit : </t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Qty.</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>OTP</t>
+  </si>
+  <si>
+    <t>12as</t>
   </si>
 </sst>
 </file>
@@ -2110,11 +2208,32 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2226,6 +2345,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -2271,7 +2396,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -2396,160 +2521,257 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="27">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -3326,27 +3548,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E17018A1-30B4-4E1F-BB8D-3F408FCF56B4}" name="DMart_Sales_Data" displayName="DMart_Sales_Data" ref="A1:P499" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E17018A1-30B4-4E1F-BB8D-3F408FCF56B4}" name="DMart_Sales_Data" displayName="DMart_Sales_Data" ref="A1:P499" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24">
   <autoFilter ref="A1:P499" xr:uid="{E17018A1-30B4-4E1F-BB8D-3F408FCF56B4}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{097F2057-1BD5-48F1-931F-E4401C805C56}" name="OrderID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{6AE4436A-01F3-4AA9-ACB7-244095DC54EF}" name="Region" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{74318643-A868-4208-B4A1-428084884C27}" name="Updated_Region" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{DFBE1467-998A-451C-8010-20864E6B4623}" name="Category" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{28A91C58-CB02-4FE7-9D6D-4D8314985E34}" name="sales" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{15B7B036-40C1-4045-83A8-22C56C2BF9A5}" name="Sales Category" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{097F2057-1BD5-48F1-931F-E4401C805C56}" name="OrderID" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{6AE4436A-01F3-4AA9-ACB7-244095DC54EF}" name="Region" dataDxfId="22"/>
+    <tableColumn id="15" xr3:uid="{74318643-A868-4208-B4A1-428084884C27}" name="Updated_Region" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{DFBE1467-998A-451C-8010-20864E6B4623}" name="Category" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{28A91C58-CB02-4FE7-9D6D-4D8314985E34}" name="sales" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{15B7B036-40C1-4045-83A8-22C56C2BF9A5}" name="Sales Category" dataDxfId="18">
       <calculatedColumnFormula>IF(DMart_Sales_Data[[#This Row],[sales]]&gt;3000,"High Sales",IF(DMart_Sales_Data[[#This Row],[sales]]&gt;1000,"Medium Sales","Low Sales"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{51F3CDC0-1345-4998-B302-EF7617264569}" name="discount" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{8E29A5B1-86B3-4DA4-98D2-B108C4687D59}" name="quantity" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{851D274F-AD48-4A3B-96C8-43B6F42BB59C}" name="order_date" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{AF2726EB-8AE1-4446-9AC3-3BA6EA1307F0}" name="delivery_date" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{7ABB3CD4-A13A-49CB-89D2-36344EA86737}" name="customer_type" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{90876443-0D83-4CAB-8181-15F50DD98A4A}" name="payment_mode" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{764F5F25-5D49-4C96-BE9D-30615B0A69A6}" name="profit" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{2799E473-9DEB-4876-8711-6F819408D820}" name="updated_city" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{FCB35956-44EE-4E95-9053-77F65881AAA7}" name="city" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{FBC69EE9-73B8-4666-B43B-700F9412C4FB}" name="Discount " dataDxfId="5">
+    <tableColumn id="5" xr3:uid="{51F3CDC0-1345-4998-B302-EF7617264569}" name="discount" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{8E29A5B1-86B3-4DA4-98D2-B108C4687D59}" name="quantity" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{851D274F-AD48-4A3B-96C8-43B6F42BB59C}" name="order_date" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{AF2726EB-8AE1-4446-9AC3-3BA6EA1307F0}" name="delivery_date" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{7ABB3CD4-A13A-49CB-89D2-36344EA86737}" name="customer_type" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{90876443-0D83-4CAB-8181-15F50DD98A4A}" name="payment_mode" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{764F5F25-5D49-4C96-BE9D-30615B0A69A6}" name="profit" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{2799E473-9DEB-4876-8711-6F819408D820}" name="updated_city" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{FCB35956-44EE-4E95-9053-77F65881AAA7}" name="city" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{FBC69EE9-73B8-4666-B43B-700F9412C4FB}" name="Discount " dataDxfId="8">
       <calculatedColumnFormula>IF(AND(DMart_Sales_Data[[#This Row],[customer_type]]="Member",OR(DMart_Sales_Data[[#This Row],[payment_mode]]="UPI",DMart_Sales_Data[[#This Row],[payment_mode]]="Card")),"Yes","No")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3552,7 +3774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1000"/>
+  <dimension ref="A1:AG1000"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -3571,8 +3793,8 @@
     <col min="15" max="15" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.6640625" customWidth="1"/>
     <col min="17" max="17" width="2.33203125" customWidth="1"/>
-    <col min="18" max="18" width="10.21875" customWidth="1"/>
-    <col min="19" max="19" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="19.5546875" customWidth="1"/>
+    <col min="19" max="19" width="13.44140625" customWidth="1"/>
     <col min="20" max="20" width="30.77734375" customWidth="1"/>
     <col min="21" max="21" width="14.44140625" customWidth="1"/>
     <col min="22" max="24" width="8.6640625" customWidth="1"/>
@@ -4259,11 +4481,11 @@
         <v>No</v>
       </c>
       <c r="Q11" s="1"/>
-      <c r="R11" s="58" t="s">
+      <c r="R11" s="72" t="s">
         <v>640</v>
       </c>
-      <c r="S11" s="58"/>
-      <c r="T11" s="58"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="72"/>
       <c r="U11" s="1">
         <f>COUNT(E2:E498)</f>
         <v>497</v>
@@ -4326,11 +4548,11 @@
         <f>IF(AND(DMart_Sales_Data[[#This Row],[customer_type]]="Member",OR(DMart_Sales_Data[[#This Row],[payment_mode]]="UPI",DMart_Sales_Data[[#This Row],[payment_mode]]="Card")),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="R12" s="59" t="s">
+      <c r="R12" s="73" t="s">
         <v>643</v>
       </c>
-      <c r="S12" s="59"/>
-      <c r="T12" s="59"/>
+      <c r="S12" s="73"/>
+      <c r="T12" s="73"/>
       <c r="U12" s="1">
         <f>COUNTIF(DMart_Sales_Data[payment_mode],"UPI")</f>
         <v>149</v>
@@ -4394,23 +4616,23 @@
         <v>No</v>
       </c>
       <c r="Q13" s="1"/>
-      <c r="R13" s="59" t="s">
+      <c r="R13" s="73" t="s">
         <v>644</v>
       </c>
-      <c r="S13" s="59"/>
-      <c r="T13" s="59"/>
+      <c r="S13" s="73"/>
+      <c r="T13" s="73"/>
       <c r="U13" s="1">
         <f>COUNTIF(DMart_Sales_Data[payment_mode],"Card")</f>
         <v>164</v>
       </c>
       <c r="V13" s="1"/>
-      <c r="W13" s="56" t="s">
+      <c r="W13" s="70" t="s">
         <v>650</v>
       </c>
-      <c r="X13" s="56"/>
-      <c r="Y13" s="56"/>
-      <c r="Z13" s="56"/>
-      <c r="AA13" s="56"/>
+      <c r="X13" s="70"/>
+      <c r="Y13" s="70"/>
+      <c r="Z13" s="70"/>
+      <c r="AA13" s="70"/>
     </row>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
@@ -4464,11 +4686,11 @@
         <v>No</v>
       </c>
       <c r="Q14" s="1"/>
-      <c r="R14" s="59" t="s">
+      <c r="R14" s="73" t="s">
         <v>645</v>
       </c>
-      <c r="S14" s="59"/>
-      <c r="T14" s="59"/>
+      <c r="S14" s="73"/>
+      <c r="T14" s="73"/>
       <c r="U14" s="1">
         <f>COUNTIF(DMart_Sales_Data[payment_mode],"Cash")</f>
         <v>185</v>
@@ -4543,9 +4765,9 @@
         <v>No</v>
       </c>
       <c r="Q15" s="1"/>
-      <c r="R15" s="58"/>
-      <c r="S15" s="58"/>
-      <c r="T15" s="58"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="44" t="s">
@@ -4610,11 +4832,11 @@
         <v>No</v>
       </c>
       <c r="Q16" s="1"/>
-      <c r="R16" s="57" t="s">
+      <c r="R16" s="71" t="s">
         <v>642</v>
       </c>
-      <c r="S16" s="57"/>
-      <c r="T16" s="57"/>
+      <c r="S16" s="71"/>
+      <c r="T16" s="71"/>
       <c r="U16" s="1">
         <f>COUNTIF(DMart_Sales_Data[sales],"&gt;4000")</f>
         <v>115</v>
@@ -4625,7 +4847,7 @@
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
     </row>
-    <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>50</v>
       </c>
@@ -4677,9 +4899,9 @@
         <v>Yes</v>
       </c>
       <c r="Q17" s="1"/>
-      <c r="R17" s="57"/>
-      <c r="S17" s="57"/>
-      <c r="T17" s="57"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="52" t="s">
@@ -4694,7 +4916,7 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>51</v>
       </c>
@@ -4746,11 +4968,11 @@
         <v>Yes</v>
       </c>
       <c r="Q18" s="1"/>
-      <c r="R18" s="57" t="s">
+      <c r="R18" s="71" t="s">
         <v>646</v>
       </c>
-      <c r="S18" s="57"/>
-      <c r="T18" s="57"/>
+      <c r="S18" s="71"/>
+      <c r="T18" s="71"/>
       <c r="U18" s="1">
         <f>COUNTIFS(DMart_Sales_Data[sales],"&gt;4000",DMart_Sales_Data[Updated_Region],"North")</f>
         <v>32</v>
@@ -4770,7 +4992,7 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>53</v>
       </c>
@@ -4822,9 +5044,9 @@
         <v>No</v>
       </c>
       <c r="Q19" s="1"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="42" t="s">
@@ -4841,7 +5063,7 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>54</v>
       </c>
@@ -4893,11 +5115,11 @@
         <v>Yes</v>
       </c>
       <c r="Q20" s="1"/>
-      <c r="R20" s="57" t="s">
+      <c r="R20" s="71" t="s">
         <v>647</v>
       </c>
-      <c r="S20" s="57"/>
-      <c r="T20" s="57"/>
+      <c r="S20" s="71"/>
+      <c r="T20" s="71"/>
       <c r="U20" s="1">
         <f>COUNTIFS(DMart_Sales_Data[sales],"&gt;4000",DMart_Sales_Data[Updated_Region],"South")</f>
         <v>27</v>
@@ -4917,7 +5139,7 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>56</v>
       </c>
@@ -4969,9 +5191,9 @@
         <v>No</v>
       </c>
       <c r="Q21" s="1"/>
-      <c r="R21" s="57"/>
-      <c r="S21" s="57"/>
-      <c r="T21" s="57"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="71"/>
+      <c r="T21" s="71"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="42" t="s">
@@ -4988,7 +5210,7 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>57</v>
       </c>
@@ -5040,11 +5262,11 @@
         <v>No</v>
       </c>
       <c r="Q22" s="1"/>
-      <c r="R22" s="57" t="s">
+      <c r="R22" s="71" t="s">
         <v>648</v>
       </c>
-      <c r="S22" s="57"/>
-      <c r="T22" s="57"/>
+      <c r="S22" s="71"/>
+      <c r="T22" s="71"/>
       <c r="U22" s="1">
         <f>COUNTIFS(DMart_Sales_Data[sales],"&gt;4000",DMart_Sales_Data[Updated_Region],"East")</f>
         <v>29</v>
@@ -5060,7 +5282,7 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>59</v>
       </c>
@@ -5112,9 +5334,9 @@
         <v>No</v>
       </c>
       <c r="Q23" s="1"/>
-      <c r="R23" s="57"/>
-      <c r="S23" s="57"/>
-      <c r="T23" s="57"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71"/>
+      <c r="T23" s="71"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -5123,7 +5345,7 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>60</v>
       </c>
@@ -5175,11 +5397,11 @@
         <v>No</v>
       </c>
       <c r="Q24" s="1"/>
-      <c r="R24" s="57" t="s">
+      <c r="R24" s="71" t="s">
         <v>649</v>
       </c>
-      <c r="S24" s="57"/>
-      <c r="T24" s="57"/>
+      <c r="S24" s="71"/>
+      <c r="T24" s="71"/>
       <c r="U24" s="1">
         <f>COUNTIFS(DMart_Sales_Data[sales],"&gt;4000",DMart_Sales_Data[Updated_Region],"West")</f>
         <v>27</v>
@@ -5198,7 +5420,7 @@
       </c>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>61</v>
       </c>
@@ -5250,9 +5472,9 @@
         <v>No</v>
       </c>
       <c r="Q25" s="1"/>
-      <c r="R25" s="57"/>
-      <c r="S25" s="57"/>
-      <c r="T25" s="57"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="71"/>
+      <c r="T25" s="71"/>
       <c r="U25" s="1"/>
       <c r="V25" s="53"/>
       <c r="W25" s="26"/>
@@ -5264,7 +5486,7 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>62</v>
       </c>
@@ -5334,7 +5556,7 @@
       </c>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>64</v>
       </c>
@@ -5386,9 +5608,15 @@
         <v>No</v>
       </c>
       <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
+      <c r="R27" s="88" t="s">
+        <v>641</v>
+      </c>
+      <c r="S27" s="88" t="s">
+        <v>578</v>
+      </c>
+      <c r="T27" s="47" t="s">
+        <v>688</v>
+      </c>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
@@ -5402,7 +5630,7 @@
       </c>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>66</v>
       </c>
@@ -5454,18 +5682,29 @@
         <v>Yes</v>
       </c>
       <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-    </row>
-    <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R28" s="89" t="s">
+        <v>61</v>
+      </c>
+      <c r="S28" s="89">
+        <f>VLOOKUP(R28,DMart_Sales_Data[[OrderID]:[sales]],MATCH(S27,DMart_Sales_Data[[#Headers],[OrderID]:[sales]],0),FALSE)</f>
+        <v>4538.1499999999996</v>
+      </c>
+      <c r="T28" s="82"/>
+      <c r="U28" s="83"/>
+      <c r="V28" s="83"/>
+      <c r="W28" s="84"/>
+      <c r="X28" s="83"/>
+      <c r="Y28" s="83"/>
+      <c r="Z28" s="85"/>
+      <c r="AA28" s="85"/>
+      <c r="AB28" s="83"/>
+      <c r="AC28" s="83"/>
+      <c r="AD28" s="83"/>
+      <c r="AE28" s="83"/>
+      <c r="AF28" s="86"/>
+      <c r="AG28" s="87"/>
+    </row>
+    <row r="29" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>67</v>
       </c>
@@ -5528,7 +5767,7 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>69</v>
       </c>
@@ -5589,7 +5828,7 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>70</v>
       </c>
@@ -5650,7 +5889,7 @@
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>71</v>
       </c>
@@ -48187,12 +48426,61 @@
     <mergeCell ref="R24:T25"/>
     <mergeCell ref="R16:T17"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="E1:F1048576">
-    <cfRule type="top10" dxfId="4" priority="2" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="3" priority="3" rank="10"/>
+    <cfRule type="top10" dxfId="7" priority="8" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="6" priority="9" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G501 G505:G1048576">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="greaterThan">
+      <formula>5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V28:W28">
+    <cfRule type="top10" dxfId="2" priority="2" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="1" priority="3" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -48211,7 +48499,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -48220,23 +48508,16 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="Y28">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R28" xr:uid="{3C3E558A-E9C3-4CD4-96E6-C37789C6AD85}">
+      <formula1>$A$2:$A$499</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <ignoredErrors>
@@ -48419,7 +48700,7 @@
       <c r="Q1" s="27" t="s">
         <v>616</v>
       </c>
-      <c r="R1" s="60" t="s">
+      <c r="R1" s="74" t="s">
         <v>617</v>
       </c>
     </row>
@@ -48446,7 +48727,7 @@
         <f>IF(AND(O2="Nagpur",P2&gt;=75),"shortlisted","Not Shortlisted")</f>
         <v>shortlisted</v>
       </c>
-      <c r="R2" s="60"/>
+      <c r="R2" s="74"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
@@ -48474,7 +48755,7 @@
         <f>IF(AND(O3="Nagpur",P3&gt;=75),"shortlisted","Not Shortlisted")</f>
         <v>Not Shortlisted</v>
       </c>
-      <c r="R3" s="60"/>
+      <c r="R3" s="74"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
@@ -48499,7 +48780,7 @@
         <f>IF(AND(O4="Nagpur",P4&gt;=75),"shortlisted","Not Shortlisted")</f>
         <v>shortlisted</v>
       </c>
-      <c r="R4" s="60"/>
+      <c r="R4" s="74"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
@@ -48524,7 +48805,7 @@
         <f>IF(AND(O5="Nagpur",P5&gt;=75),"shortlisted","Not Shortlisted")</f>
         <v>Not Shortlisted</v>
       </c>
-      <c r="R5" s="60"/>
+      <c r="R5" s="74"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E6" s="25" t="s">
@@ -48579,7 +48860,7 @@
         <f>IF(E11&gt;=50000,"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G11" s="61" t="s">
+      <c r="G11" s="75" t="s">
         <v>618</v>
       </c>
       <c r="H11" s="28" t="s">
@@ -48598,7 +48879,7 @@
         <f>IF(AND(I11&gt;=75,J11&gt;=75),"A+","A")</f>
         <v>A+</v>
       </c>
-      <c r="M11" s="60" t="s">
+      <c r="M11" s="74" t="s">
         <v>617</v>
       </c>
     </row>
@@ -48613,7 +48894,7 @@
         <f t="shared" ref="F12:F20" si="0">IF(E12&gt;=50000,"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G12" s="61"/>
+      <c r="G12" s="75"/>
       <c r="H12" s="28" t="s">
         <v>609</v>
       </c>
@@ -48630,10 +48911,10 @@
         <f>IF(AND(I12&gt;=75,J12&gt;=75),"A+","A")</f>
         <v>A</v>
       </c>
-      <c r="M12" s="60"/>
+      <c r="M12" s="74"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="74" t="s">
         <v>619</v>
       </c>
       <c r="D13" s="28" t="s">
@@ -48646,7 +48927,7 @@
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="G13" s="61"/>
+      <c r="G13" s="75"/>
       <c r="H13" s="28" t="s">
         <v>610</v>
       </c>
@@ -48663,10 +48944,10 @@
         <f>IF(AND(I13&gt;=75,J13&gt;=75),"A+","A")</f>
         <v>A</v>
       </c>
-      <c r="M13" s="60"/>
+      <c r="M13" s="74"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="60"/>
+      <c r="B14" s="74"/>
       <c r="D14" s="28" t="s">
         <v>595</v>
       </c>
@@ -48677,7 +48958,7 @@
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="G14" s="61"/>
+      <c r="G14" s="75"/>
       <c r="H14" s="28" t="s">
         <v>611</v>
       </c>
@@ -48694,10 +48975,10 @@
         <f>IF(AND(I14&gt;=75,J14&gt;=75),"A+","A")</f>
         <v>A+</v>
       </c>
-      <c r="M14" s="60"/>
+      <c r="M14" s="74"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="60"/>
+      <c r="B15" s="74"/>
       <c r="D15" s="28" t="s">
         <v>597</v>
       </c>
@@ -48708,7 +48989,7 @@
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="G15" s="61"/>
+      <c r="G15" s="75"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D16" s="28" t="s">
@@ -48721,7 +49002,7 @@
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="G16" s="61"/>
+      <c r="G16" s="75"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D17" s="28" t="s">
@@ -48734,7 +49015,7 @@
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="G17" s="61"/>
+      <c r="G17" s="75"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D18" s="28" t="s">
@@ -48747,7 +49028,7 @@
         <f t="shared" si="0"/>
         <v>No</v>
       </c>
-      <c r="G18" s="61"/>
+      <c r="G18" s="75"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D19" s="28" t="s">
@@ -48760,7 +49041,7 @@
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="G19" s="61"/>
+      <c r="G19" s="75"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D20" s="28" t="s">
@@ -48773,7 +49054,7 @@
         <f t="shared" si="0"/>
         <v>Yes</v>
       </c>
-      <c r="G20" s="61"/>
+      <c r="G20" s="75"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="L21" s="27" t="s">
@@ -49014,12 +49295,12 @@
     <mergeCell ref="G11:G20"/>
     <mergeCell ref="B13:B15"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="E11:E20">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>55350</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>50000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49240,63 +49521,66 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E968D9CD-0407-43A7-952B-97D5DF189B2C}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>600</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C9" s="62" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C9" s="76" t="s">
         <v>664</v>
       </c>
-      <c r="D9" s="62"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D9" s="76"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>678</v>
+      </c>
       <c r="C10">
         <f>SUBTOTAL(9,A2:A8)</f>
         <v>2150</v>
@@ -49305,8 +49589,14 @@
         <f>SUBTOTAL(109,A2:A8)</f>
         <v>2150</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>679</v>
+      </c>
       <c r="C11">
         <f>SUBTOTAL(1,A2:A8)</f>
         <v>307.14285714285717</v>
@@ -49314,6 +49604,9 @@
       <c r="D11">
         <f>SUBTOTAL(101,A2:A8)</f>
         <v>307.14285714285717</v>
+      </c>
+      <c r="E11" t="s">
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -49321,7 +49614,7 @@
   <mergeCells count="1">
     <mergeCell ref="C9:D9"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -49336,19 +49629,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="58" t="s">
         <v>672</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="58" t="s">
         <v>603</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="58" t="s">
         <v>578</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="58" t="s">
         <v>630</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="58" t="s">
         <v>633</v>
       </c>
     </row>
@@ -49404,7 +49697,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="64">
+      <c r="A5" s="57">
         <v>1004</v>
       </c>
       <c r="B5" s="29" t="s">
@@ -49421,7 +49714,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="64">
+      <c r="A6" s="57">
         <v>1005</v>
       </c>
       <c r="B6" s="29" t="s">
@@ -49442,35 +49735,35 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="25"/>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="48" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="25"/>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="60" t="s">
         <v>673</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="61" t="s">
         <v>578</v>
       </c>
-      <c r="D11" s="68" t="s">
+      <c r="D11" s="61" t="s">
         <v>633</v>
       </c>
-      <c r="E11" s="68" t="s">
+      <c r="E11" s="61" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="25"/>
-      <c r="B12" s="66">
+      <c r="B12" s="59">
         <v>1004</v>
       </c>
-      <c r="C12" s="66">
+      <c r="C12" s="59">
         <f>VLOOKUP(B12,A2:E6,MATCH("Sales",A1:E1,0),FALSE)</f>
         <v>75000</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="59">
         <f>VLOOKUP(B12,A2:E6,MATCH("Bonus Amount",A1:E1,0),FALSE)</f>
         <v>11250</v>
       </c>
@@ -49484,7 +49777,7 @@
         <f>MATCH(B2,B2:B6,0)</f>
         <v>1</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="56" t="s">
         <v>674</v>
       </c>
     </row>
@@ -49493,7 +49786,7 @@
         <f>MATCH("Bonus Amount",A1:E1,0)</f>
         <v>5</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="56" t="s">
         <v>675</v>
       </c>
     </row>
@@ -49503,13 +49796,13 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="62" t="s">
         <v>673</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="63" t="s">
         <v>578</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="63" t="s">
         <v>633</v>
       </c>
     </row>
@@ -49537,7 +49830,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12 B19" xr:uid="{6DD947B4-1704-413E-8511-E8C10400EAE4}">
       <formula1>$A$2:$A$6</formula1>
@@ -49545,4 +49838,530 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0069D601-0FDE-41C5-A5D2-02518EC19071}">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="64"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="35"/>
+      <c r="B2" s="37" t="s">
+        <v>682</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>683</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>684</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>685</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="37" t="s">
+        <v>686</v>
+      </c>
+      <c r="B3" s="35">
+        <v>100</v>
+      </c>
+      <c r="C3" s="35">
+        <v>585</v>
+      </c>
+      <c r="D3" s="35">
+        <v>333</v>
+      </c>
+      <c r="E3" s="35">
+        <v>745</v>
+      </c>
+      <c r="F3" s="35">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="37" t="s">
+        <v>687</v>
+      </c>
+      <c r="B4" s="35">
+        <v>100</v>
+      </c>
+      <c r="C4" s="35">
+        <v>500</v>
+      </c>
+      <c r="D4" s="35">
+        <v>600</v>
+      </c>
+      <c r="E4" s="35">
+        <v>700</v>
+      </c>
+      <c r="F4" s="35">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="37" t="s">
+        <v>578</v>
+      </c>
+      <c r="B5" s="35">
+        <v>2000</v>
+      </c>
+      <c r="C5" s="35">
+        <v>7000</v>
+      </c>
+      <c r="D5" s="35">
+        <v>8000</v>
+      </c>
+      <c r="E5" s="35">
+        <v>6000</v>
+      </c>
+      <c r="F5" s="35">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="37" t="s">
+        <v>688</v>
+      </c>
+      <c r="B6" s="35">
+        <v>400</v>
+      </c>
+      <c r="C6" s="35">
+        <v>500</v>
+      </c>
+      <c r="D6" s="35">
+        <v>300</v>
+      </c>
+      <c r="E6" s="35">
+        <v>300</v>
+      </c>
+      <c r="F6" s="35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="64" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="37" t="s">
+        <v>689</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>685</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="37" t="s">
+        <v>578</v>
+      </c>
+      <c r="C9" s="35">
+        <f>HLOOKUP($C$8,$B$2:$F$6,MATCH(B9,$A$2:$A$6,FALSE),FALSE)</f>
+        <v>6000</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>689</v>
+      </c>
+      <c r="H9" s="66" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="37" t="s">
+        <v>687</v>
+      </c>
+      <c r="C10" s="35">
+        <f t="shared" ref="C10:C12" si="0">HLOOKUP($C$8,$B$2:$F$6,MATCH(B10,$A$2:$A$6,FALSE),FALSE)</f>
+        <v>700</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>578</v>
+      </c>
+      <c r="H10" s="29">
+        <f>VLOOKUP(G10,A3:F6,MATCH(H9,A2:F2,0),FALSE)</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="37" t="s">
+        <v>686</v>
+      </c>
+      <c r="C11" s="35">
+        <f t="shared" si="0"/>
+        <v>745</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="37" t="s">
+        <v>688</v>
+      </c>
+      <c r="C12" s="35">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40671B3-4CDB-402E-9BAE-A07C3874E29B}">
+  <dimension ref="A1:S14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>693</v>
+      </c>
+      <c r="C1" cm="1">
+        <f t="array" aca="1" ref="C1" ca="1">INDIRECT(B1)+10</f>
+        <v>14</v>
+      </c>
+      <c r="M1" s="35"/>
+      <c r="N1" s="67" t="s">
+        <v>698</v>
+      </c>
+      <c r="O1" s="67" t="s">
+        <v>699</v>
+      </c>
+      <c r="P1" s="67" t="s">
+        <v>700</v>
+      </c>
+      <c r="R1" s="69" t="s">
+        <v>701</v>
+      </c>
+      <c r="S1" s="69" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>697</v>
+      </c>
+      <c r="N2" s="35">
+        <v>55</v>
+      </c>
+      <c r="O2" s="35">
+        <v>44</v>
+      </c>
+      <c r="P2" s="35">
+        <v>44</v>
+      </c>
+      <c r="R2" s="68" t="s">
+        <v>702</v>
+      </c>
+      <c r="S2">
+        <f ca="1">SUM(INDIRECT(S1))</f>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C3" cm="1">
+        <f t="array" aca="1" ref="C3" ca="1">INDIRECT("A2")+100</f>
+        <v>105</v>
+      </c>
+      <c r="M3" s="37" t="s">
+        <v>586</v>
+      </c>
+      <c r="N3" s="35">
+        <v>33</v>
+      </c>
+      <c r="O3" s="35">
+        <v>32</v>
+      </c>
+      <c r="P3" s="35">
+        <v>66</v>
+      </c>
+      <c r="R3" s="68" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="M4" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="N4" s="35">
+        <v>45</v>
+      </c>
+      <c r="O4" s="35">
+        <v>50</v>
+      </c>
+      <c r="P4" s="35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>111</v>
+      </c>
+      <c r="C5" t="s">
+        <v>694</v>
+      </c>
+      <c r="E5" cm="1">
+        <f t="array" aca="1" ref="E5" ca="1">INDIRECT(C5)</f>
+        <v>111</v>
+      </c>
+      <c r="M5" s="37" t="s">
+        <v>589</v>
+      </c>
+      <c r="N5" s="35">
+        <v>34</v>
+      </c>
+      <c r="O5" s="35">
+        <v>32</v>
+      </c>
+      <c r="P5" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>222</v>
+      </c>
+      <c r="M6" s="37" t="s">
+        <v>590</v>
+      </c>
+      <c r="N6" s="35">
+        <v>21</v>
+      </c>
+      <c r="O6" s="35">
+        <v>26</v>
+      </c>
+      <c r="P6" s="35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>333</v>
+      </c>
+      <c r="C7" t="s">
+        <v>695</v>
+      </c>
+      <c r="E7" cm="1">
+        <f t="array" aca="1" ref="E7" ca="1">INDIRECT(C7,FALSE)</f>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>585</v>
+      </c>
+      <c r="B12" t="s">
+        <v>549</v>
+      </c>
+      <c r="C12" t="str">
+        <f>A12&amp;"  "&amp;B12</f>
+        <v>Ankit  Sharma</v>
+      </c>
+      <c r="D12" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0293808-E06D-4B70-8A55-179F6E6B4BA3}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="79" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1" s="79" t="s">
+        <v>705</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>706</v>
+      </c>
+      <c r="D1" s="78" t="s">
+        <v>613</v>
+      </c>
+      <c r="E1" s="78" t="s">
+        <v>613</v>
+      </c>
+      <c r="F1" s="78" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="35">
+        <v>21</v>
+      </c>
+      <c r="B2" s="35">
+        <v>10</v>
+      </c>
+      <c r="C2" s="77">
+        <v>46217</v>
+      </c>
+      <c r="D2" s="35">
+        <v>71</v>
+      </c>
+      <c r="E2" s="80">
+        <v>45</v>
+      </c>
+      <c r="F2" s="81" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="35">
+        <v>18</v>
+      </c>
+      <c r="B3" s="35">
+        <v>9</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35">
+        <v>45</v>
+      </c>
+      <c r="E3" s="80">
+        <v>47</v>
+      </c>
+      <c r="F3" s="35">
+        <v>4561</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="35">
+        <v>60</v>
+      </c>
+      <c r="B4" s="35">
+        <v>8</v>
+      </c>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35">
+        <v>75</v>
+      </c>
+      <c r="E4" s="35"/>
+      <c r="F4" s="81"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="35">
+        <v>21</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35">
+        <v>67</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" t="b">
+        <f>AND(E2&gt;40,E2&lt;=75)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="35">
+        <v>19</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35">
+        <v>45</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="80">
+        <v>48</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="80">
+        <v>18</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="80">
+        <v>16</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+    </row>
+  </sheetData>
+  <dataValidations count="8">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Age Error" error="Entered age is not in range" sqref="A1:A1048576" xr:uid="{4EC44A1E-3087-4CB3-B943-6FC84E64908D}">
+      <formula1>18</formula1>
+      <formula2>60</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Quantity" error="only allowed betwwen 2-10 " prompt="Enter Qty Between 2 to 10" sqref="B10:B11" xr:uid="{E00FDA15-CB11-483B-8163-7916B8F7490F}">
+      <formula1>2</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Quantity Error" error="Invalid Entry For Quantity" promptTitle="Quantity" prompt="Enter Quantity Between 2 to 10" sqref="B2:B9" xr:uid="{4EFF8708-F89F-4689-B979-0ABF5458774C}">
+      <formula1>2</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10:C11" xr:uid="{7A9A7518-E3F6-44CE-B250-88EACA58C57B}">
+      <formula1>46218</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Date Error" error="You Cannot Enter Future Date" promptTitle="Date" prompt="Enter Date Before Today" sqref="C2:C9" xr:uid="{DD161CBF-A344-4ACC-BD20-2A2EED30D554}">
+      <formula1>46218</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Only Enter Between 41 to 75" promptTitle="Marks" prompt="Enter Between 41 to 75" sqref="D2:D9" xr:uid="{72478F7A-8874-4CFA-BF92-824F8EC0E2CA}">
+      <formula1>41</formula1>
+      <formula2>75</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2 E4:E9 E3" xr:uid="{8C3F89A4-4D2F-4A50-A24E-96C7798E48DA}">
+      <formula1>AND(E2&gt;40,E2&lt;=75)</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Incorrect OTP" error="You Have Entered Wrong OTP" promptTitle="OTP" prompt="Enter OTP Recieved 4 Character" sqref="F2:F9" xr:uid="{1542C505-9655-415B-967F-601F6F399C8B}">
+      <formula1>4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>